--- a/output/pdf_financials_xlsx/TBLL.xlsx
+++ b/output/pdf_financials_xlsx/TBLL.xlsx
@@ -5403,31 +5403,31 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.02988</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.02988</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.02988</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.02988</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.02988</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.02988</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.02988</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.02988</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.02988</v>
       </c>
       <c r="L92" s="3" t="n">
         <v>0</v>
@@ -10978,7 +10978,11 @@
           <t>Reserve 5</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -11785,7 +11789,11 @@
           <t>Reserve 5</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -12321,7 +12329,11 @@
           <t>Reserve 4</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -12762,7 +12774,11 @@
           <t>Reserve 4</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
@@ -13128,7 +13144,11 @@
           <t>Reserve 4</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -14754,7 +14774,11 @@
           <t>Share based payment reserve 6</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
@@ -14843,7 +14867,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TBLL.xlsx
+++ b/output/pdf_financials_xlsx/TBLL.xlsx
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000461</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.001054</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000259</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -1003,19 +1003,19 @@
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.008744</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.004828</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>5e-06</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.025916</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.000278</v>
       </c>
     </row>
     <row r="13">
@@ -1844,13 +1844,13 @@
         <v>-0.013709</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.150546</v>
+        <v>-0.151007</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.10226</v>
+        <v>-0.103314</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.061977</v>
+        <v>-0.062236</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-0.040326</v>
@@ -1871,19 +1871,19 @@
         <v>-0.031687</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-11.297362</v>
+        <v>-11.306106</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-2.961971</v>
+        <v>-2.966799</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.38573</v>
+        <v>-0.385735</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.613968</v>
+        <v>-0.639884</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.462868</v>
+        <v>-0.463146</v>
       </c>
     </row>
     <row r="28">
@@ -1948,13 +1948,13 @@
         <v>-0.013709</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.150546</v>
+        <v>-0.151007</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.10226</v>
+        <v>-0.103314</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.061977</v>
+        <v>-0.062236</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-0.040326</v>
@@ -1975,19 +1975,19 @@
         <v>-0.031687</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-11.291298</v>
+        <v>-11.300042</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-2.939633</v>
+        <v>-2.944461</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.380121</v>
+        <v>-0.380126</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.610192</v>
+        <v>-0.636108</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.462868</v>
+        <v>-0.463146</v>
       </c>
     </row>
     <row r="30">
@@ -2220,34 +2220,34 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.086591</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.018057</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.009320999999999999</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.00758</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.0031</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.000354</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.055807</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.016235</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.268306</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.003388</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>2.280688</v>
@@ -2262,7 +2262,7 @@
         <v>0.00413</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.004096</v>
       </c>
     </row>
     <row r="35">
@@ -2324,34 +2324,34 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.086591</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.15</v>
+        <v>0.168057</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.075</v>
+        <v>0.08432099999999999</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.00758</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.0031</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.000354</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.055807</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.016235</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.268306</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.003388</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>2.280688</v>
@@ -2366,7 +2366,7 @@
         <v>0.37413</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.17875</v>
+        <v>0.182846</v>
       </c>
     </row>
     <row r="37">
@@ -2948,34 +2948,34 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.086591</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.018057</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.014174</v>
+        <v>0.004853</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.008389000000000001</v>
+        <v>0.000809</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.003538</v>
+        <v>0.000438</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.000792</v>
+        <v>0.000438</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.05669</v>
+        <v>0.000883</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.01696</v>
+        <v>0.000725</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.269107</v>
+        <v>0.000801</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.00387</v>
+        <v>0.000482</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>0.104368</v>
@@ -2990,7 +2990,7 @@
         <v>0.019288</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.02105</v>
+        <v>0.016954</v>
       </c>
     </row>
     <row r="49">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -15047,7 +15047,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E82" s="5" t="n">
@@ -24701,7 +24701,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -25706,7 +25706,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -28534,7 +28534,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">

--- a/output/pdf_financials_xlsx/TBLL.xlsx
+++ b/output/pdf_financials_xlsx/TBLL.xlsx
@@ -1263,10 +1263,10 @@
         <v>-0</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0.769628</v>
+        <v>-0.769628</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>0.271666</v>
+        <v>-0.271666</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>-0</v>
@@ -3860,31 +3860,31 @@
         <v>0.011888</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.031031</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.004682</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.013451</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.026715</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.001051</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.000967</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>0.001569</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>0.015298</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>0.074918</v>
       </c>
       <c r="M64" s="3" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>0.023869</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0.038031</v>
+        <v>0.069062</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0.011682</v>
+        <v>0.016364</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.020951</v>
+        <v>0.034402</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.034215</v>
+        <v>0.06093</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0.009551</v>
+        <v>0.010602</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0.009467</v>
+        <v>0.010434</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.011019</v>
+        <v>0.012588</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0.024298</v>
+        <v>0.039596</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>1.481589</v>
+        <v>1.556507</v>
       </c>
       <c r="M68" s="3" t="n">
         <v>0.311348</v>
@@ -4435,16 +4435,16 @@
         <v>0</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>0.007365</v>
+        <v>0.002683</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.033525</v>
+        <v>0.020074</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.040625</v>
+        <v>0.01391</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.001784</v>
+        <v>0.000733</v>
       </c>
       <c r="I75" s="3" t="n">
         <v>0</v>
@@ -4453,7 +4453,7 @@
         <v>0.25838</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>0.033796</v>
+        <v>0.018498</v>
       </c>
       <c r="L75" s="3" t="n">
         <v>0</v>
@@ -16309,7 +16309,11 @@
           <t>Private placements</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>-</t>
@@ -17933,7 +17937,11 @@
           <t>Deferred income tax recovery 7</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>
@@ -22409,7 +22417,11 @@
           <t>Common shares issued for cash</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E164" s="5" t="n">
         <v>0.102</v>
       </c>
@@ -26240,7 +26252,11 @@
           <t>Deferred income tax recovery 11</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
@@ -27146,7 +27162,11 @@
           <t>Deferred income tax recovery 7</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E217" t="inlineStr">
         <is>
           <t>-</t>
